--- a/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21391</t>
+          <t>21298</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34416</t>
+          <t>34684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41820</t>
+          <t>40913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60731</t>
+          <t>59921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>48914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61701</t>
+          <t>61619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54048</t>
+          <t>53780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67073</t>
+          <t>67166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106292</t>
+          <t>107102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125203</t>
+          <t>126110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47146</t>
+          <t>47346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68203</t>
+          <t>67171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>55957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76758</t>
+          <t>77079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108601</t>
+          <t>107986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139214</t>
+          <t>138494</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119043</t>
+          <t>120075</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>140100</t>
+          <t>139900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111973</t>
+          <t>111652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132676</t>
+          <t>132774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>236763</t>
+          <t>237483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267376</t>
+          <t>267991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>25185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>39429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33842</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50638</t>
+          <t>51651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62554</t>
+          <t>63890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86170</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45878</t>
+          <t>47050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61803</t>
+          <t>61294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52623</t>
+          <t>51610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69419</t>
+          <t>68511</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103570</t>
+          <t>104196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127186</t>
+          <t>125850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44597</t>
+          <t>43587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64107</t>
+          <t>64091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52194</t>
+          <t>52662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71094</t>
+          <t>72465</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101584</t>
+          <t>101429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129588</t>
+          <t>127773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86968</t>
+          <t>86984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106478</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77000</t>
+          <t>75629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95900</t>
+          <t>95432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169581</t>
+          <t>171396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>197585</t>
+          <t>197740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149513</t>
+          <t>148119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>182265</t>
+          <t>182107</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>179082</t>
+          <t>179464</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>213526</t>
+          <t>214454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338020</t>
+          <t>337770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>386435</t>
+          <t>388260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>321094</t>
+          <t>321252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>353846</t>
+          <t>355240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>315023</t>
+          <t>314095</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349467</t>
+          <t>349085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>645473</t>
+          <t>643648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>693888</t>
+          <t>694138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39281</t>
+          <t>40428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30528</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47472</t>
+          <t>47549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59342</t>
+          <t>60198</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82581</t>
+          <t>82242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>63693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79027</t>
+          <t>80327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64571</t>
+          <t>64494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81515</t>
+          <t>82050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133582</t>
+          <t>133921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156821</t>
+          <t>155965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45250</t>
+          <t>46378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64669</t>
+          <t>65524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47393</t>
+          <t>46812</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67907</t>
+          <t>67663</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98205</t>
+          <t>97080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128202</t>
+          <t>126561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94675</t>
+          <t>93820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114094</t>
+          <t>112966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125317</t>
+          <t>125561</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145831</t>
+          <t>146412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224366</t>
+          <t>226007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>254363</t>
+          <t>255488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30926</t>
+          <t>31334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47919</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31928</t>
+          <t>32118</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47765</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67489</t>
+          <t>68670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91360</t>
+          <t>91598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50061</t>
+          <t>50741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67054</t>
+          <t>66646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54047</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69884</t>
+          <t>69694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108433</t>
+          <t>108195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132304</t>
+          <t>131123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34960</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52089</t>
+          <t>52337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44366</t>
+          <t>44450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63105</t>
+          <t>63239</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84017</t>
+          <t>83923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109433</t>
+          <t>108757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63431</t>
+          <t>63183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80560</t>
+          <t>81706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68597</t>
+          <t>68463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87336</t>
+          <t>87252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137788</t>
+          <t>138464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163204</t>
+          <t>163298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,05%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153090</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187837</t>
+          <t>186219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172586</t>
+          <t>172497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>208284</t>
+          <t>208367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333641</t>
+          <t>333254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>385221</t>
+          <t>384731</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>289128</t>
+          <t>290746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>323875</t>
+          <t>323868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>330497</t>
+          <t>330414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>366195</t>
+          <t>366284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>630525</t>
+          <t>631015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>682105</t>
+          <t>682492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>24202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48162</t>
+          <t>48443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68606</t>
+          <t>68655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68515</t>
+          <t>67704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81620</t>
+          <t>81695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60150</t>
+          <t>59385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74745</t>
+          <t>74065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132365</t>
+          <t>132316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152809</t>
+          <t>152528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38413</t>
+          <t>38235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55660</t>
+          <t>56746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51916</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73499</t>
+          <t>74555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97179</t>
+          <t>97247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126022</t>
+          <t>126131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100605</t>
+          <t>99519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117852</t>
+          <t>118030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137093</t>
+          <t>136037</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158676</t>
+          <t>157471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240835</t>
+          <t>240726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269678</t>
+          <t>269610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>39160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56943</t>
+          <t>58499</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40161</t>
+          <t>40818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58622</t>
+          <t>58913</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84354</t>
+          <t>83737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111405</t>
+          <t>109116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87371</t>
+          <t>85815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105393</t>
+          <t>105154</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73549</t>
+          <t>73258</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92010</t>
+          <t>91353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165080</t>
+          <t>167369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192131</t>
+          <t>192748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48118</t>
+          <t>47396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66836</t>
+          <t>66681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37233</t>
+          <t>37394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56267</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91527</t>
+          <t>90553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117992</t>
+          <t>117734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55270</t>
+          <t>55425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73988</t>
+          <t>74710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73737</t>
+          <t>74031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92771</t>
+          <t>92610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134118</t>
+          <t>134376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160583</t>
+          <t>161557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>163082</t>
+          <t>162427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198848</t>
+          <t>199215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173316</t>
+          <t>169476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207870</t>
+          <t>207926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342393</t>
+          <t>346326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393868</t>
+          <t>396908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326542</t>
+          <t>326175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>362308</t>
+          <t>362963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>363163</t>
+          <t>363107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>397717</t>
+          <t>401557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>702555</t>
+          <t>699515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>754030</t>
+          <t>750097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45395</t>
+          <t>45607</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52847</t>
+          <t>52905</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44226</t>
+          <t>44187</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54059</t>
+          <t>54212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>92762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105108</t>
+          <t>105294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17218</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26361</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112639</t>
+          <t>113082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130729</t>
+          <t>130627</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130787</t>
+          <t>131623</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150571</t>
+          <t>150934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249892</t>
+          <t>251076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276603</t>
+          <t>276670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46660</t>
+          <t>46217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31983</t>
+          <t>31620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51767</t>
+          <t>50931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65250</t>
+          <t>65183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91961</t>
+          <t>90777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127991</t>
+          <t>127973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147033</t>
+          <t>146531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147997</t>
+          <t>149654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172647</t>
+          <t>171808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>283435</t>
+          <t>284567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313117</t>
+          <t>314253</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>27357</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45897</t>
+          <t>45915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>40682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64493</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73261</t>
+          <t>72125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102943</t>
+          <t>101811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>191867</t>
+          <t>190325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228755</t>
+          <t>227500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>193343</t>
+          <t>193722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243081</t>
+          <t>243344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>398387</t>
+          <t>400082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>460291</t>
+          <t>460614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46703</t>
+          <t>47958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83591</t>
+          <t>85133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62402</t>
+          <t>62139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112140</t>
+          <t>111761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>120649</t>
+          <t>120326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182553</t>
+          <t>180858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>495054</t>
+          <t>494793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>541281</t>
+          <t>542431</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>543841</t>
+          <t>545068</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>602518</t>
+          <t>601628</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1058540</t>
+          <t>1053870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1130723</t>
+          <t>1125460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124874</t>
+          <t>123724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171101</t>
+          <t>171362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159454</t>
+          <t>160344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218131</t>
+          <t>216904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>297404</t>
+          <t>302667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369587</t>
+          <t>374257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27741</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20162</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34772</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,79%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>22950</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16940</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29645</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17271</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29725</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29,21%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>27741</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21298</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>34684</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31,36%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40913</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>59439</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60723</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53692</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>68,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55609</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48914</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>61619</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48834</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>61288</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>70,79%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60723</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53780</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>67166</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>68,64%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107102</t>
+          <t>107584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126110</t>
+          <t>125941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66007</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>55548</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>76793</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>57343</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>47346</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>67171</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>48260</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>69430</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,62%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>66007</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>55957</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>77079</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107986</t>
+          <t>109658</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138494</t>
+          <t>138855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>122724</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>111938</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>133183</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>129903</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>120075</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>139900</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>117816</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>138986</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>122724</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>111652</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>132774</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237483</t>
+          <t>237122</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267991</t>
+          <t>266319</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42116</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34599</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49841</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>32057</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25185</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39429</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>24915</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39785</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42116</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>34750</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51651</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>40,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63890</t>
+          <t>63691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85544</t>
+          <t>84432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,5%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61145</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53420</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>68662</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>59,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>66,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>54422</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>47050</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>61294</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46694</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>61564</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>62,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>61145</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>51610</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>68511</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>59,21%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104196</t>
+          <t>105308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125850</t>
+          <t>126049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,43%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>61347</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>52033</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>70268</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>53285</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43587</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>64091</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43967</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>62680</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>61347</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>52662</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>72465</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>101257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127773</t>
+          <t>128846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>86747</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77826</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>96061</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>97790</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>86984</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>107488</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>88395</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>107108</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>64,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>86747</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75629</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>95432</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171396</t>
+          <t>170323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>197740</t>
+          <t>197912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>179147</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>213532</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>165636</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>148119</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>182107</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>149198</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>182885</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>197211</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>179464</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>214454</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337770</t>
+          <t>338740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388260</t>
+          <t>388537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>331338</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>315017</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>349402</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>62,69%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>337723</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>321252</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>355240</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>320474</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>354161</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>67,09%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>331338</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>314095</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>349085</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>62,69%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>643648</t>
+          <t>643371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>694138</t>
+          <t>693168</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38883</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30469</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47051</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>27,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>31949</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23794</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40428</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24104</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39427</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,68%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38883</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29993</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>47549</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>34,7%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60198</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82242</t>
+          <t>82160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>73160</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64992</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>81574</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>72,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>72172</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>63693</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80327</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>64694</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80017</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>69,32%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73160</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>64494</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82050</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>65,3%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133921</t>
+          <t>134003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155965</t>
+          <t>156173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>57272</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>45976</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68563</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>35,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54896</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>46378</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>65524</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>44574</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>65483</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,45%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>41,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>57272</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>46812</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67663</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97080</t>
+          <t>98559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126561</t>
+          <t>125754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>135952</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>124661</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>147248</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104448</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>93820</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>112966</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>93861</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>114770</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,55%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>135952</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>125561</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>146412</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>226007</t>
+          <t>226814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255488</t>
+          <t>254009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39953</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31695</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48007</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>39290</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31334</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47239</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31683</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>47272</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,1%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39953</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32118</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>48325</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68670</t>
+          <t>67003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91598</t>
+          <t>89750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61859</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53805</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>70117</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>52,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>68,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>58690</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>50741</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>66646</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>50708</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>66297</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>59,9%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>51,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>68,02%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>61859</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>53487</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69694</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>60,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108195</t>
+          <t>110043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>132790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53210</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44279</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61913</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>42936</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>33814</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52337</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34119</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>51131</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>37,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>53210</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44450</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>63239</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>40,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83923</t>
+          <t>83219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108757</t>
+          <t>107532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78492</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>69789</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>87423</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>72584</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>63183</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>81706</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>64389</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>81401</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>62,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78492</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>68463</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>87252</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>59,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138464</t>
+          <t>139689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163298</t>
+          <t>164002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>171369</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>208553</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>38,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>169071</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>153097</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>186219</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>151473</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>186786</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>189318</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>172497</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>208367</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333254</t>
+          <t>332062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>384731</t>
+          <t>381335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>349463</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>330228</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>367412</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>64,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>61,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>68,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>446</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>307894</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>290746</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>323868</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>290179</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>325492</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>64,55%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>60,96%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>349463</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>330414</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>366284</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>64,86%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>631015</t>
+          <t>634411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>682492</t>
+          <t>683684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31124</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24257</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38369</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31,67%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27404</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21009</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35000</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20516</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34471</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26,68%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>31124</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24202</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38882</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31,67%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48443</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68655</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67143</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59898</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74010</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>68,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>75300</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67704</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>81695</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>68233</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>73,32%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>65,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67143</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>59385</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74065</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>68,33%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132316</t>
+          <t>132321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152528</t>
+          <t>152618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>63441</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53209</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>74975</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>46814</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38235</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56746</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>37896</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>56703</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>29,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>63441</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>53121</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>74555</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97247</t>
+          <t>96884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126131</t>
+          <t>126310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>147151</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>135617</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>157383</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>109451</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99519</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>118030</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>99562</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>118369</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>70,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>147151</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>136037</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>157471</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>69,88%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240726</t>
+          <t>240547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269610</t>
+          <t>269973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49181</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39357</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>57170</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>43,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>47613</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39160</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>58499</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>38337</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56766</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,99%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>49181</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>40818</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58913</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83737</t>
+          <t>84365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109116</t>
+          <t>109140</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>82990</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75001</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>92814</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>62,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>56,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>96701</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85815</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>105154</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>87548</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>105977</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>67,01%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>82990</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73258</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>91353</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>62,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167369</t>
+          <t>167345</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192748</t>
+          <t>192120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>46597</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37966</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>55684</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>57313</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>47396</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>66681</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>47788</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>66009</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>46,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>38,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>54,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>46597</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>37394</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>55973</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>35,84%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90553</t>
+          <t>91288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117734</t>
+          <t>119005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>83407</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74320</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>92038</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,16%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>70,8%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>64793</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>55425</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>74710</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>56097</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>74318</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,06%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>45,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>61,18%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>83407</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>74031</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>92610</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>64,16%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134376</t>
+          <t>133105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161557</t>
+          <t>160822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>172936</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>210538</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>179144</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>162427</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>199215</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>161254</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>195993</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>37,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>190343</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>169476</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>207926</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>346326</t>
+          <t>343486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>396908</t>
+          <t>397367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>380690</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>360495</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>398097</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>346246</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>326175</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>362963</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>329397</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>364136</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>62,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>69,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>380690</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>363107</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>401557</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,67%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>699515</t>
+          <t>699056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>750097</t>
+          <t>752937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41376</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37135</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44632</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>81,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>49913</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45607</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52905</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>79,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>45143</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44187</t>
+          <t>41169</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54212</t>
+          <t>48088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>99609</t>
+          <t>86519</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92762</t>
+          <t>81186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105294</t>
+          <t>91006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9161</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7598</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4606</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>124240</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>115649</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>131333</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>83,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>122079</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>113082</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>130627</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>76,64%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>82,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>141645</t>
+          <t>110151</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131623</t>
+          <t>101929</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150934</t>
+          <t>118121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>263724</t>
+          <t>234390</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>251076</t>
+          <t>223261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276670</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,0%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33282</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26189</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41873</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>37220</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28672</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46217</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40909</t>
+          <t>35367</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31620</t>
+          <t>27397</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50931</t>
+          <t>43589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>78129</t>
+          <t>68649</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65183</t>
+          <t>57572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90777</t>
+          <t>79778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>138428</t>
+          <t>151505</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127973</t>
+          <t>139087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146531</t>
+          <t>162075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>160666</t>
+          <t>140015</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149654</t>
+          <t>129717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171808</t>
+          <t>147956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>299094</t>
+          <t>291520</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284567</t>
+          <t>275532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314253</t>
+          <t>303470</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48621</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>38051</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>61039</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>35460</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27357</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45915</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51824</t>
+          <t>35503</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40682</t>
+          <t>27562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62836</t>
+          <t>45801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>87284</t>
+          <t>84124</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72125</t>
+          <t>72174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101811</t>
+          <t>100112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>221920</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>199062</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>238500</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>68,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>208326</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>190325</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>227500</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>224441</t>
+          <t>192601</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>193722</t>
+          <t>181133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243344</t>
+          <t>203773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>432767</t>
+          <t>414521</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>400082</t>
+          <t>391314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>460614</t>
+          <t>434475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>54145</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>93583</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>31,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>67132</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47958</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>85133</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>81042</t>
+          <t>63952</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62139</t>
+          <t>52780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111761</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>148173</t>
+          <t>134677</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>120326</t>
+          <t>114723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180858</t>
+          <t>157884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>539040</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>512446</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>559254</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>76,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>73,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>518745</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>494793</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>542431</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>81,43%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>576450</t>
+          <t>487909</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>545068</t>
+          <t>470432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>601628</t>
+          <t>505171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1095195</t>
+          <t>1026950</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1053870</t>
+          <t>996381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1125460</t>
+          <t>1055093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>147410</t>
+          <t>161789</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123724</t>
+          <t>141575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171362</t>
+          <t>188383</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>185522</t>
+          <t>141769</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160344</t>
+          <t>124507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216904</t>
+          <t>159246</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>332932</t>
+          <t>303558</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302667</t>
+          <t>275415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374257</t>
+          <t>334127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
